--- a/fixtures/files/intelliplan_timmar_MBAB_2026-09.xlsx
+++ b/fixtures/files/intelliplan_timmar_MBAB_2026-09.xlsx
@@ -470,7 +470,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E5" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F5" t="str">
         <v>1/9 2026</v>
@@ -496,7 +496,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E6" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F6" s="1">
         <v>46267</v>
@@ -522,7 +522,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E7" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F7" t="str">
         <v>5/9 2026</v>
@@ -548,7 +548,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E8" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F8" s="1">
         <v>46277</v>
@@ -574,7 +574,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E9" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F9" s="1">
         <v>46281</v>
@@ -600,7 +600,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E10" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F10" s="1">
         <v>46282</v>
@@ -626,7 +626,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E11" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F11" s="1">
         <v>46286</v>
@@ -652,7 +652,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E12" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F12" t="str">
         <v>24/9 2026</v>
@@ -678,7 +678,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E13" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F13" s="1">
         <v>46291</v>
@@ -704,7 +704,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E14" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F14" t="str">
         <v>2026-09-28</v>
@@ -730,7 +730,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E15" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F15" s="1">
         <v>46267</v>
@@ -756,7 +756,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E16" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F16" s="1">
         <v>46268</v>
@@ -782,7 +782,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E17" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F17" t="str">
         <v>6/9 2026</v>
@@ -808,7 +808,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E18" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F18" s="1">
         <v>46272</v>
@@ -834,7 +834,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E19" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F19" t="str">
         <v>13/9 2026</v>
@@ -860,7 +860,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E20" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F20" t="str">
         <v>14/9 2026</v>
@@ -886,7 +886,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E21" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F21" s="1">
         <v>46281</v>
@@ -912,7 +912,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E22" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F22" s="1">
         <v>46289</v>
@@ -938,7 +938,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E23" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F23" s="1">
         <v>46290</v>
@@ -964,7 +964,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E24" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F24" t="str">
         <v>2026-09-26</v>
@@ -990,7 +990,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E25" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F25" s="1">
         <v>46267</v>
@@ -1016,7 +1016,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E26" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F26" s="1">
         <v>46268</v>
@@ -1042,7 +1042,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E27" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F27" t="str">
         <v>4/9 2026</v>
@@ -1068,7 +1068,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E28" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F28" t="str">
         <v>6/9 2026</v>
@@ -1094,7 +1094,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E29" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F29" s="1">
         <v>46278</v>
@@ -1120,7 +1120,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E30" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F30" t="str">
         <v>15/9 2026</v>
@@ -1146,7 +1146,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E31" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F31" s="1">
         <v>46281</v>
@@ -1172,7 +1172,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E32" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F32" t="str">
         <v>21/9 2026</v>
@@ -1198,7 +1198,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E33" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F33" s="1">
         <v>46287</v>
@@ -1224,7 +1224,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E34" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F34" t="str">
         <v>23/9 2026</v>
@@ -1250,7 +1250,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E35" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F35" s="1">
         <v>46291</v>
@@ -1276,7 +1276,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E36" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F36" s="1">
         <v>46295</v>
@@ -1302,7 +1302,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E37" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F37" s="1">
         <v>46268</v>
@@ -1328,7 +1328,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E38" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F38" t="str">
         <v>4/9 2026</v>
@@ -1354,7 +1354,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E39" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F39" s="1">
         <v>46270</v>
@@ -1380,7 +1380,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E40" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F40" s="1">
         <v>46275</v>
@@ -1406,7 +1406,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E41" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F41" t="str">
         <v>11/9 2026</v>
@@ -1432,7 +1432,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E42" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F42" s="1">
         <v>46277</v>
@@ -1458,7 +1458,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E43" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F43" s="1">
         <v>46284</v>
@@ -1484,7 +1484,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E44" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F44" s="1">
         <v>46286</v>
@@ -1510,7 +1510,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E45" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F45" s="1">
         <v>46287</v>
@@ -1536,7 +1536,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E46" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F46" t="str">
         <v>23/9 2026</v>
@@ -1562,7 +1562,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E47" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F47" s="1">
         <v>46291</v>
@@ -1588,7 +1588,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E48" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F48" t="str">
         <v>28/9 2026</v>
@@ -1614,7 +1614,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E49" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F49" s="1">
         <v>46295</v>
@@ -1640,7 +1640,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E50" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F50" s="1">
         <v>46267</v>
@@ -1666,7 +1666,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E51" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F51" s="1">
         <v>46268</v>
@@ -1692,7 +1692,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E52" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F52" s="1">
         <v>46270</v>
@@ -1718,7 +1718,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E53" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F53" s="1">
         <v>46271</v>
@@ -1744,7 +1744,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E54" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F54" s="1">
         <v>46273</v>
@@ -1770,7 +1770,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E55" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F55" s="1">
         <v>46276</v>
@@ -1796,7 +1796,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E56" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F56" s="1">
         <v>46278</v>
@@ -1822,7 +1822,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E57" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F57" s="1">
         <v>46280</v>
@@ -1848,7 +1848,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E58" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F58" s="1">
         <v>46286</v>
@@ -1874,7 +1874,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="E59" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="F59" t="str">
         <v>24/9 2026</v>
@@ -1900,7 +1900,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E60" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F60" s="1">
         <v>46272</v>
@@ -1926,7 +1926,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E61" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F61" s="1">
         <v>46276</v>
@@ -1952,7 +1952,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E62" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F62" s="1">
         <v>46267</v>
@@ -1978,7 +1978,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E63" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F63" s="1">
         <v>46269</v>
@@ -2004,7 +2004,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E64" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F64" s="1">
         <v>46278</v>
@@ -2030,7 +2030,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E65" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F65" s="1">
         <v>46279</v>
@@ -2056,7 +2056,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E66" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F66" s="1">
         <v>46284</v>
@@ -2082,7 +2082,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E67" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F67" s="1">
         <v>46288</v>
@@ -2108,7 +2108,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E68" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F68" t="str">
         <v>28/9 2026</v>
@@ -2134,7 +2134,7 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="E69" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="F69" s="1">
         <v>46294</v>
@@ -2160,7 +2160,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E71" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F71" t="str">
         <v>2/9 2026</v>
@@ -2186,7 +2186,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E72" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F72" s="1">
         <v>46269</v>
@@ -2212,7 +2212,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E73" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F73" s="1">
         <v>46270</v>
@@ -2238,7 +2238,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E74" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F74" s="1">
         <v>46274</v>
@@ -2264,7 +2264,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E75" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F75" s="1">
         <v>46275</v>
@@ -2290,7 +2290,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E76" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F76" t="str">
         <v>2026-09-13</v>
@@ -2316,7 +2316,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E77" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F77" s="1">
         <v>46279</v>
@@ -2342,7 +2342,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E78" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F78" t="str">
         <v>16/9 2026</v>
@@ -2368,7 +2368,7 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="E79" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="F79" t="str">
         <v>2026-09-17</v>
@@ -2394,7 +2394,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E80" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F80" t="str">
         <v>2026-09-05</v>
@@ -2420,7 +2420,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E81" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F81" t="str">
         <v>8/9 2026</v>
@@ -2446,7 +2446,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E82" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F82" s="1">
         <v>46279</v>
@@ -2472,7 +2472,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E83" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F83" t="str">
         <v>21/9 2026</v>
@@ -2498,7 +2498,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E84" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F84" t="str">
         <v>2026-09-23</v>
@@ -2524,7 +2524,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E85" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F85" s="1">
         <v>46289</v>
@@ -2550,7 +2550,7 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="E86" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="F86" s="1">
         <v>46295</v>
@@ -2576,7 +2576,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E87" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F87" t="str">
         <v>2026-09-09</v>
@@ -2602,7 +2602,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E88" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F88" t="str">
         <v>2026-09-15</v>
@@ -2628,7 +2628,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E89" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F89" s="1">
         <v>46287</v>
@@ -2654,7 +2654,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E90" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F90" s="1">
         <v>46292</v>
@@ -2680,7 +2680,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E91" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F91" t="str">
         <v>2/9 2026</v>
@@ -2706,7 +2706,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E92" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F92" t="str">
         <v>3/9 2026</v>
@@ -2732,7 +2732,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E93" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F93" s="1">
         <v>46269</v>
@@ -2758,7 +2758,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E94" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F94" s="1">
         <v>46270</v>
@@ -2784,7 +2784,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E95" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F95" s="1">
         <v>46273</v>
@@ -2810,7 +2810,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E96" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F96" t="str">
         <v>2026-09-09</v>
@@ -2836,7 +2836,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E97" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F97" s="1">
         <v>46278</v>
@@ -2862,7 +2862,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E98" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F98" s="1">
         <v>46279</v>
@@ -2888,7 +2888,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E99" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F99" s="1">
         <v>46281</v>
@@ -2914,7 +2914,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E100" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F100" s="1">
         <v>46283</v>
@@ -2940,7 +2940,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E101" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F101" s="1">
         <v>46286</v>
@@ -2966,7 +2966,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E102" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F102" t="str">
         <v>2026-09-28</v>
@@ -2992,7 +2992,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E103" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F103" s="1">
         <v>46266</v>
@@ -3018,7 +3018,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E104" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F104" s="1">
         <v>46280</v>
@@ -3044,7 +3044,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E105" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F105" t="str">
         <v>16/9 2026</v>
@@ -3070,7 +3070,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E106" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F106" s="1">
         <v>46288</v>
@@ -3096,7 +3096,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E107" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F107" s="1">
         <v>46289</v>
@@ -3122,7 +3122,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E108" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F108" s="1">
         <v>46294</v>
@@ -3148,7 +3148,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E109" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F109" s="1">
         <v>46295</v>
@@ -3174,7 +3174,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E110" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F110" s="1">
         <v>46273</v>
@@ -3200,7 +3200,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E111" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F111" s="1">
         <v>46274</v>
@@ -3226,7 +3226,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E112" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F112" t="str">
         <v>16/9 2026</v>
@@ -3252,7 +3252,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E113" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F113" t="str">
         <v>2026-09-24</v>
@@ -3278,7 +3278,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E114" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F114" s="1">
         <v>46290</v>
@@ -3304,7 +3304,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E115" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F115" t="str">
         <v>28/9 2026</v>
@@ -3330,7 +3330,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E116" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F116" t="str">
         <v>30/9 2026</v>
@@ -3376,7 +3376,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E119" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F119" s="1">
         <v>46267</v>
@@ -3402,7 +3402,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E120" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F120" t="str">
         <v>2026-09-05</v>
@@ -3428,7 +3428,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E121" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F121" t="str">
         <v>9/9 2026</v>
@@ -3454,7 +3454,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E122" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F122" s="1">
         <v>46291</v>
@@ -3480,7 +3480,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E123" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F123" s="1">
         <v>46292</v>
@@ -3506,7 +3506,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E124" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F124" t="str">
         <v>28/9 2026</v>
@@ -3532,7 +3532,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E125" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F125" s="1">
         <v>46267</v>
@@ -3558,7 +3558,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E126" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F126" s="1">
         <v>46271</v>
@@ -3584,7 +3584,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E127" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F127" s="1">
         <v>46273</v>
@@ -3610,7 +3610,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E128" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F128" s="1">
         <v>46279</v>
@@ -3636,7 +3636,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E129" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F129" s="1">
         <v>46281</v>
@@ -3662,7 +3662,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E130" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F130" t="str">
         <v>17/9 2026</v>
@@ -3688,7 +3688,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E131" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F131" t="str">
         <v>2026-09-21</v>
@@ -3714,7 +3714,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E132" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F132" s="1">
         <v>46293</v>
@@ -3740,7 +3740,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E133" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F133" s="1">
         <v>46266</v>
@@ -3766,7 +3766,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E134" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F134" s="1">
         <v>46267</v>
@@ -3792,7 +3792,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E135" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F135" t="str">
         <v>3/9 2026</v>
@@ -3818,7 +3818,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E136" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F136" s="1">
         <v>46270</v>
@@ -3844,7 +3844,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E137" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F137" s="1">
         <v>46271</v>
@@ -3870,7 +3870,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E138" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F138" s="1">
         <v>46272</v>
@@ -3896,7 +3896,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E139" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F139" s="1">
         <v>46274</v>
@@ -3922,7 +3922,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E140" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F140" s="1">
         <v>46275</v>
@@ -3948,7 +3948,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E141" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F141" s="1">
         <v>46278</v>
@@ -3974,7 +3974,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E142" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F142" s="1">
         <v>46279</v>
@@ -4000,7 +4000,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E143" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F143" s="1">
         <v>46280</v>
@@ -4026,7 +4026,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E144" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F144" s="1">
         <v>46281</v>
@@ -4052,7 +4052,7 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="E145" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="F145" s="1">
         <v>46282</v>
@@ -4078,7 +4078,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E146" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F146" s="1">
         <v>46267</v>
@@ -4104,7 +4104,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E147" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F147" s="1">
         <v>46268</v>
@@ -4130,7 +4130,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E148" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F148" t="str">
         <v>3/9 2026</v>
@@ -4156,7 +4156,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E149" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F149" t="str">
         <v>6/9 2026</v>
@@ -4182,7 +4182,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E150" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F150" s="1">
         <v>46274</v>
@@ -4208,7 +4208,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E151" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F151" t="str">
         <v>13/9 2026</v>
@@ -4234,7 +4234,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E152" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F152" t="str">
         <v>17/9 2026</v>
@@ -4260,7 +4260,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E153" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F153" t="str">
         <v>20/9 2026</v>
@@ -4286,7 +4286,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E154" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F154" s="1">
         <v>46288</v>
@@ -4312,7 +4312,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E155" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F155" s="1">
         <v>46270</v>
@@ -4338,7 +4338,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E156" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F156" t="str">
         <v>21/9 2026</v>
@@ -4384,7 +4384,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E158" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F158" t="str">
         <v>2026-09-03</v>
@@ -4410,7 +4410,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E159" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F159" s="1">
         <v>46271</v>
@@ -4436,7 +4436,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E160" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F160" s="1">
         <v>46272</v>
@@ -4462,7 +4462,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E161" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F161" t="str">
         <v>20/9 2026</v>
@@ -4488,7 +4488,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E162" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F162" t="str">
         <v>2026-09-04</v>
@@ -4514,7 +4514,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E163" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F163" t="str">
         <v>2026-09-08</v>
@@ -4540,7 +4540,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E164" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F164" s="1">
         <v>46278</v>
@@ -4566,7 +4566,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E165" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F165" s="1">
         <v>46284</v>
@@ -4592,7 +4592,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E166" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F166" s="1">
         <v>46286</v>
@@ -4618,7 +4618,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E167" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F167" s="1">
         <v>46287</v>
@@ -4644,7 +4644,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E168" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F168" t="str">
         <v>23/9 2026</v>
@@ -4670,7 +4670,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E169" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F169" s="1">
         <v>46293</v>
@@ -4696,7 +4696,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E170" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F170" s="1">
         <v>46294</v>
@@ -4722,7 +4722,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E171" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F171" s="1">
         <v>46272</v>
@@ -4748,7 +4748,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E172" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F172" t="str">
         <v>8/9 2026</v>
@@ -4774,7 +4774,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E173" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F173" s="1">
         <v>46274</v>
@@ -4800,7 +4800,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E174" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F174" s="1">
         <v>46276</v>
@@ -4826,7 +4826,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E175" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F175" t="str">
         <v>12/9 2026</v>
@@ -4852,7 +4852,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E176" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F176" s="1">
         <v>46278</v>
@@ -4878,7 +4878,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E177" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F177" s="1">
         <v>46279</v>
@@ -4904,7 +4904,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E178" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F178" s="1">
         <v>46281</v>
@@ -4930,7 +4930,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E179" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F179" t="str">
         <v>17/9 2026</v>
@@ -4956,7 +4956,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E180" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F180" t="str">
         <v>19/9 2026</v>
@@ -4982,7 +4982,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E181" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F181" t="str">
         <v>2026-09-27</v>
@@ -5008,7 +5008,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E182" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F182" s="1">
         <v>46293</v>
@@ -5034,7 +5034,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E183" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F183" s="1">
         <v>46266</v>
@@ -5060,7 +5060,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E184" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F184" s="1">
         <v>46269</v>
@@ -5086,7 +5086,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E185" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F185" s="1">
         <v>46282</v>
@@ -5112,7 +5112,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E186" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F186" t="str">
         <v>2026-09-19</v>
@@ -5138,7 +5138,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E187" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F187" t="str">
         <v>26/9 2026</v>
@@ -5164,7 +5164,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E189" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F189" s="1">
         <v>46273</v>
@@ -5190,7 +5190,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E190" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F190" s="1">
         <v>46274</v>
@@ -5216,7 +5216,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E191" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F191" s="1">
         <v>46279</v>
@@ -5242,7 +5242,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E192" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F192" s="1">
         <v>46284</v>
@@ -5268,7 +5268,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E193" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F193" s="1">
         <v>46285</v>
@@ -5294,7 +5294,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E194" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F194" s="1">
         <v>46290</v>
@@ -5320,7 +5320,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E195" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F195" s="1">
         <v>46291</v>
@@ -5346,7 +5346,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E196" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F196" s="1">
         <v>46294</v>
@@ -5372,7 +5372,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E197" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F197" s="1">
         <v>46267</v>
@@ -5398,7 +5398,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E198" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F198" t="str">
         <v>8/9 2026</v>
@@ -5424,7 +5424,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E199" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F199" s="1">
         <v>46276</v>
@@ -5450,7 +5450,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E200" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F200" t="str">
         <v>12/9 2026</v>
@@ -5476,7 +5476,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E201" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F201" s="1">
         <v>46279</v>
@@ -5502,7 +5502,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E202" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F202" s="1">
         <v>46282</v>
@@ -5528,7 +5528,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E203" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F203" s="1">
         <v>46287</v>
@@ -5554,7 +5554,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E204" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F204" s="1">
         <v>46292</v>
@@ -5580,7 +5580,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E205" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F205" s="1">
         <v>46293</v>
@@ -5606,7 +5606,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E206" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F206" s="1">
         <v>46277</v>
@@ -5632,7 +5632,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E207" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F207" s="1">
         <v>46279</v>
@@ -5658,7 +5658,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E208" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F208" t="str">
         <v>2026-09-17</v>
@@ -5684,7 +5684,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E209" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F209" s="1">
         <v>46284</v>
@@ -5710,7 +5710,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E210" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F210" s="1">
         <v>46290</v>
@@ -5736,7 +5736,7 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="E211" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="F211" s="1">
         <v>46291</v>
@@ -5762,7 +5762,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E212" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F212" t="str">
         <v>2/9 2026</v>
@@ -5788,7 +5788,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E213" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F213" s="1">
         <v>46271</v>
@@ -5814,7 +5814,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E214" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F214" t="str">
         <v>10/9 2026</v>
@@ -5840,7 +5840,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E215" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F215" t="str">
         <v>12/9 2026</v>
@@ -5866,7 +5866,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E216" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F216" t="str">
         <v>13/9 2026</v>
@@ -5892,7 +5892,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E217" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F217" s="1">
         <v>46281</v>
@@ -5918,7 +5918,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E218" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F218" t="str">
         <v>18/9 2026</v>
@@ -5944,7 +5944,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E219" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F219" s="1">
         <v>46286</v>
@@ -5970,7 +5970,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E220" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F220" t="str">
         <v>23/9 2026</v>
@@ -5996,7 +5996,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E221" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F221" s="1">
         <v>46291</v>
@@ -6022,7 +6022,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E222" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F222" s="1">
         <v>46292</v>
@@ -6048,7 +6048,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E223" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F223" s="1">
         <v>46293</v>
@@ -6074,7 +6074,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E224" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F224" s="1">
         <v>46294</v>
@@ -6100,7 +6100,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E225" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F225" t="str">
         <v>21/9 2026</v>
@@ -6126,7 +6126,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E226" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F226" s="1">
         <v>46287</v>
@@ -6152,7 +6152,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E227" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F227" s="1">
         <v>46288</v>
@@ -6178,7 +6178,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E228" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F228" t="str">
         <v>2026-09-24</v>
@@ -6204,7 +6204,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E229" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F229" s="1">
         <v>46290</v>
@@ -6230,7 +6230,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E230" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F230" s="1">
         <v>46291</v>
@@ -6256,7 +6256,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E231" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F231" t="str">
         <v>27/9 2026</v>
@@ -6282,7 +6282,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E232" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F232" s="1">
         <v>46293</v>
@@ -6308,7 +6308,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E233" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F233" s="1">
         <v>46294</v>
@@ -6334,7 +6334,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="E234" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="F234" t="str">
         <v>30/9 2026</v>
@@ -6360,7 +6360,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E235" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F235" s="1">
         <v>46271</v>
@@ -6386,7 +6386,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E236" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F236" s="1">
         <v>46272</v>
@@ -6412,7 +6412,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E237" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F237" t="str">
         <v>11/9 2026</v>
@@ -6438,7 +6438,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E238" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F238" s="1">
         <v>46277</v>
@@ -6464,7 +6464,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E239" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F239" t="str">
         <v>2026-09-16</v>
@@ -6490,7 +6490,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E240" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F240" s="1">
         <v>46287</v>
@@ -6516,7 +6516,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E241" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F241" t="str">
         <v>2026-09-23</v>
@@ -6542,7 +6542,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E242" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F242" t="str">
         <v>26/9 2026</v>
@@ -6568,7 +6568,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E243" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F243" s="1">
         <v>46293</v>
@@ -6594,7 +6594,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E244" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F244" s="1">
         <v>46273</v>
@@ -6620,7 +6620,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E245" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F245" s="1">
         <v>46275</v>
@@ -6646,7 +6646,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E246" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F246" s="1">
         <v>46276</v>
@@ -6672,7 +6672,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E247" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F247" s="1">
         <v>46277</v>
@@ -6698,7 +6698,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E248" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F248" s="1">
         <v>46279</v>
@@ -6724,7 +6724,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E249" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F249" t="str">
         <v>2026-09-15</v>
@@ -6750,7 +6750,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E250" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F250" s="1">
         <v>46282</v>
@@ -6776,7 +6776,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E251" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F251" t="str">
         <v>18/9 2026</v>
@@ -6802,7 +6802,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E252" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F252" s="1">
         <v>46284</v>
@@ -6828,7 +6828,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E253" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F253" s="1">
         <v>46285</v>
@@ -6854,7 +6854,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E254" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F254" s="1">
         <v>46287</v>
@@ -6880,7 +6880,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E255" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F255" s="1">
         <v>46290</v>
@@ -6906,7 +6906,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E256" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F256" t="str">
         <v>29/9 2026</v>
@@ -6932,7 +6932,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E257" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F257" s="1">
         <v>46295</v>
@@ -6978,7 +6978,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E259" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F259" s="1">
         <v>46276</v>
@@ -7004,7 +7004,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E260" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F260" s="1">
         <v>46278</v>
@@ -7030,7 +7030,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E261" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F261" s="1">
         <v>46279</v>
@@ -7056,7 +7056,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E262" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F262" s="1">
         <v>46288</v>
@@ -7082,7 +7082,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E263" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F263" s="1">
         <v>46275</v>
@@ -7108,7 +7108,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E264" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F264" t="str">
         <v>12/9 2026</v>
@@ -7134,7 +7134,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E265" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F265" s="1">
         <v>46280</v>
@@ -7160,7 +7160,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E266" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F266" s="1">
         <v>46282</v>
@@ -7186,7 +7186,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E267" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F267" s="1">
         <v>46283</v>
@@ -7212,7 +7212,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E268" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F268" t="str">
         <v>2026-09-19</v>
@@ -7238,7 +7238,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E269" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F269" s="1">
         <v>46285</v>
@@ -7264,7 +7264,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E270" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F270" t="str">
         <v>21/9 2026</v>
@@ -7290,7 +7290,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E271" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F271" s="1">
         <v>46287</v>
@@ -7316,7 +7316,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E272" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F272" s="1">
         <v>46288</v>
@@ -7342,7 +7342,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E273" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F273" s="1">
         <v>46291</v>
@@ -7368,7 +7368,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E274" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F274" s="1">
         <v>46293</v>
@@ -7394,7 +7394,7 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="E275" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="F275" s="1">
         <v>46295</v>
@@ -7420,7 +7420,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E276" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F276" s="1">
         <v>46266</v>
@@ -7446,7 +7446,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E277" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F277" s="1">
         <v>46267</v>
@@ -7472,7 +7472,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E278" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F278" t="str">
         <v>26/9 2026</v>
@@ -7498,7 +7498,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E279" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F279" s="1">
         <v>46293</v>
@@ -7682,7 +7682,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E289" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F289" t="str">
         <v>2026-09-14</v>
@@ -7708,7 +7708,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E290" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F290" s="1">
         <v>46293</v>
@@ -7734,7 +7734,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E291" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F291" s="1">
         <v>46295</v>
@@ -7760,7 +7760,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E292" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F292" t="str">
         <v>2026-09-01</v>
@@ -7786,7 +7786,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="E293" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="F293" s="1">
         <v>46283</v>
@@ -7812,7 +7812,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E294" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F294" s="1">
         <v>46271</v>
@@ -7838,7 +7838,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E295" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F295" s="1">
         <v>46279</v>
@@ -7864,7 +7864,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E296" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F296" s="1">
         <v>46289</v>
@@ -7890,7 +7890,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E297" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F297" s="1">
         <v>46266</v>
@@ -7916,7 +7916,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E298" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F298" t="str">
         <v>2/9 2026</v>
@@ -7942,7 +7942,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E299" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F299" t="str">
         <v>7/9 2026</v>
@@ -7968,7 +7968,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E300" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F300" t="str">
         <v>2026-09-08</v>
@@ -7994,7 +7994,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E301" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F301" t="str">
         <v>12/9 2026</v>
@@ -8020,7 +8020,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E302" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F302" t="str">
         <v>2026-09-14</v>
@@ -8046,7 +8046,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E303" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F303" s="1">
         <v>46280</v>
@@ -8072,7 +8072,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E304" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F304" s="1">
         <v>46281</v>
@@ -8098,7 +8098,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E305" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F305" t="str">
         <v>20/9 2026</v>
@@ -8124,7 +8124,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E306" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F306" s="1">
         <v>46286</v>
@@ -8150,7 +8150,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E307" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F307" t="str">
         <v>22/9 2026</v>
@@ -8176,7 +8176,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E308" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F308" t="str">
         <v>26/9 2026</v>
@@ -8202,7 +8202,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E309" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F309" s="1">
         <v>46293</v>
@@ -8228,7 +8228,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E310" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F310" t="str">
         <v>25/9 2026</v>
@@ -8254,7 +8254,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E311" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F311" t="str">
         <v>26/9 2026</v>
@@ -8280,7 +8280,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E312" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F312" t="str">
         <v>2026-09-27</v>
@@ -8306,7 +8306,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E313" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F313" t="str">
         <v>28/9 2026</v>
@@ -8332,7 +8332,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E314" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F314" s="1">
         <v>46294</v>
@@ -8358,7 +8358,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="E315" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="F315" s="1">
         <v>46295</v>
@@ -8384,7 +8384,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E316" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F316" s="1">
         <v>46269</v>
@@ -8410,7 +8410,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E317" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F317" s="1">
         <v>46270</v>
@@ -8436,7 +8436,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E318" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F318" s="1">
         <v>46280</v>
@@ -8462,7 +8462,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E319" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F319" t="str">
         <v>2026-09-17</v>
@@ -8488,7 +8488,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E320" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F320" s="1">
         <v>46284</v>
@@ -8514,7 +8514,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E321" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F321" s="1">
         <v>46285</v>
@@ -8540,7 +8540,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E322" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F322" s="1">
         <v>46289</v>
@@ -8566,7 +8566,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E323" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F323" s="1">
         <v>46290</v>
@@ -8592,7 +8592,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E324" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F324" t="str">
         <v>28/9 2026</v>
@@ -8618,7 +8618,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E325" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F325" s="1">
         <v>46294</v>
@@ -8664,7 +8664,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E328" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F328" s="1">
         <v>46272</v>
@@ -8690,7 +8690,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E329" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F329" s="1">
         <v>46289</v>
@@ -8716,7 +8716,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E330" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F330" s="1">
         <v>46270</v>
@@ -8742,7 +8742,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E331" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F331" s="1">
         <v>46274</v>
@@ -8768,7 +8768,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E332" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F332" t="str">
         <v>11/9 2026</v>
@@ -8794,7 +8794,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E333" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F333" s="1">
         <v>46277</v>
@@ -8820,7 +8820,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E334" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F334" s="1">
         <v>46279</v>
@@ -8846,7 +8846,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E335" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F335" s="1">
         <v>46295</v>
@@ -8872,7 +8872,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="E336" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="F336" s="1">
         <v>46272</v>
@@ -8898,7 +8898,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="E337" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="F337" s="1">
         <v>46275</v>
@@ -8924,7 +8924,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="E338" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="F338" s="1">
         <v>46281</v>
@@ -8950,7 +8950,7 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="E339" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="F339" s="1">
         <v>46288</v>
@@ -8976,7 +8976,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E340" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F340" s="1">
         <v>46267</v>
@@ -9002,7 +9002,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E341" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F341" t="str">
         <v>3/9 2026</v>
@@ -9028,7 +9028,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E342" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F342" s="1">
         <v>46273</v>
@@ -9054,7 +9054,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E343" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F343" t="str">
         <v>13/9 2026</v>
@@ -9080,7 +9080,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E344" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F344" t="str">
         <v>14/9 2026</v>
@@ -9106,7 +9106,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E345" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F345" s="1">
         <v>46282</v>
@@ -9132,7 +9132,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E346" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F346" t="str">
         <v>2026-09-18</v>
@@ -9158,7 +9158,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E347" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F347" s="1">
         <v>46288</v>
@@ -9184,7 +9184,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E348" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F348" s="1">
         <v>46289</v>
@@ -9210,7 +9210,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E349" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F349" t="str">
         <v>26/9 2026</v>
@@ -9316,7 +9316,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E354" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F354" s="1">
         <v>46270</v>
@@ -9342,7 +9342,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E355" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F355" s="1">
         <v>46272</v>
@@ -9368,7 +9368,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E356" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F356" t="str">
         <v>2026-09-08</v>
@@ -9394,7 +9394,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E357" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F357" s="1">
         <v>46277</v>
@@ -9420,7 +9420,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E358" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F358" s="1">
         <v>46278</v>
@@ -9446,7 +9446,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E359" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F359" s="1">
         <v>46279</v>
@@ -9472,7 +9472,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E360" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F360" s="1">
         <v>46280</v>
@@ -9498,7 +9498,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E361" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F361" s="1">
         <v>46282</v>
@@ -9524,7 +9524,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E362" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F362" s="1">
         <v>46284</v>
@@ -9550,7 +9550,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E363" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F363" s="1">
         <v>46285</v>
@@ -9576,7 +9576,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E364" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F364" s="1">
         <v>46287</v>
@@ -9602,7 +9602,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E365" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F365" s="1">
         <v>46290</v>
@@ -9628,7 +9628,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E366" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F366" s="1">
         <v>46292</v>
@@ -9654,7 +9654,7 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="E367" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="F367" t="str">
         <v>28/9 2026</v>
@@ -9680,7 +9680,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="E369" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="F369" s="1">
         <v>46266</v>
@@ -9706,7 +9706,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="E370" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="F370" t="str">
         <v>2026-09-15</v>
@@ -9732,7 +9732,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="E371" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="F371" t="str">
         <v>16/9 2026</v>
@@ -9758,7 +9758,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="E372" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="F372" s="1">
         <v>46285</v>
@@ -9784,7 +9784,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E373" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F373" s="1">
         <v>46266</v>
@@ -9810,7 +9810,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E374" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F374" s="1">
         <v>46267</v>
@@ -9836,7 +9836,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E375" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F375" s="1">
         <v>46273</v>
@@ -9862,7 +9862,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E376" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F376" t="str">
         <v>12/9 2026</v>
@@ -9888,7 +9888,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E377" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F377" t="str">
         <v>13/9 2026</v>
@@ -9914,7 +9914,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E378" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F378" s="1">
         <v>46280</v>
@@ -9940,7 +9940,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E379" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F379" s="1">
         <v>46281</v>
@@ -9966,7 +9966,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E380" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F380" t="str">
         <v>18/9 2026</v>
@@ -9992,7 +9992,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E381" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F381" s="1">
         <v>46284</v>
@@ -10018,7 +10018,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E382" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F382" s="1">
         <v>46288</v>
@@ -10044,7 +10044,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E383" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F383" s="1">
         <v>46293</v>
@@ -10070,7 +10070,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E384" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F384" s="1">
         <v>46295</v>
@@ -10096,7 +10096,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E385" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F385" s="1">
         <v>46269</v>
@@ -10122,7 +10122,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E386" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F386" s="1">
         <v>46271</v>
@@ -10148,7 +10148,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E387" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F387" t="str">
         <v>8/9 2026</v>
@@ -10174,7 +10174,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E388" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F388" s="1">
         <v>46276</v>
@@ -10200,7 +10200,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E389" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F389" s="1">
         <v>46284</v>
@@ -10226,7 +10226,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E390" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F390" s="1">
         <v>46288</v>
@@ -10252,7 +10252,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E391" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F391" t="str">
         <v>2026-09-24</v>
@@ -10278,7 +10278,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E392" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F392" s="1">
         <v>46266</v>
@@ -10304,7 +10304,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E393" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F393" t="str">
         <v>2026-09-01</v>
@@ -10330,7 +10330,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E394" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F394" s="1">
         <v>46275</v>
@@ -10356,7 +10356,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E395" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F395" s="1">
         <v>46278</v>
@@ -10382,7 +10382,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E396" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F396" s="1">
         <v>46288</v>
@@ -10408,7 +10408,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E397" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F397" s="1">
         <v>46291</v>
@@ -10434,7 +10434,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E398" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F398" s="1">
         <v>46293</v>
@@ -10460,7 +10460,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E399" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F399" s="1">
         <v>46294</v>
@@ -10486,7 +10486,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E400" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F400" t="str">
         <v>2026-09-02</v>
@@ -10512,7 +10512,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E401" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F401" s="1">
         <v>46274</v>
@@ -10538,7 +10538,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E402" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F402" s="1">
         <v>46277</v>
@@ -10564,7 +10564,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E403" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F403" t="str">
         <v>13/9 2026</v>
@@ -10590,7 +10590,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E404" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F404" s="1">
         <v>46284</v>
@@ -10616,7 +10616,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E405" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F405" t="str">
         <v>27/9 2026</v>
@@ -10642,7 +10642,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E406" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F406" s="1">
         <v>46267</v>
@@ -10668,7 +10668,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E407" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F407" s="1">
         <v>46268</v>
@@ -10694,7 +10694,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E408" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F408" t="str">
         <v>7/9 2026</v>
@@ -10720,7 +10720,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E409" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F409" s="1">
         <v>46273</v>
@@ -10746,7 +10746,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E410" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F410" s="1">
         <v>46274</v>
@@ -10772,7 +10772,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E411" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F411" s="1">
         <v>46275</v>
@@ -10798,7 +10798,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E412" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F412" t="str">
         <v>2026-09-11</v>
@@ -10824,7 +10824,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E413" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F413" s="1">
         <v>46278</v>
@@ -10850,7 +10850,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E414" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F414" s="1">
         <v>46266</v>
@@ -10876,7 +10876,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E415" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F415" s="1">
         <v>46269</v>
@@ -10902,7 +10902,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E416" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F416" t="str">
         <v>2026-09-07</v>
@@ -10928,7 +10928,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E417" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F417" s="1">
         <v>46275</v>
@@ -10954,7 +10954,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E418" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F418" s="1">
         <v>46278</v>
@@ -10980,7 +10980,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E419" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F419" t="str">
         <v>2026-09-24</v>
@@ -11006,7 +11006,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="E420" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="F420" t="str">
         <v>30/9 2026</v>
@@ -11032,7 +11032,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E422" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F422" s="1">
         <v>46268</v>
@@ -11058,7 +11058,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E423" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F423" t="str">
         <v>4/9 2026</v>
@@ -11084,7 +11084,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E424" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F424" s="1">
         <v>46270</v>
@@ -11110,7 +11110,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E425" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F425" s="1">
         <v>46276</v>
@@ -11136,7 +11136,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E426" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F426" s="1">
         <v>46279</v>
@@ -11162,7 +11162,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E427" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F427" s="1">
         <v>46282</v>
@@ -11188,7 +11188,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E428" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F428" s="1">
         <v>46285</v>
@@ -11214,7 +11214,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E429" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F429" s="1">
         <v>46289</v>
@@ -11240,7 +11240,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E430" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F430" t="str">
         <v>26/9 2026</v>
@@ -11266,7 +11266,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E431" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F431" t="str">
         <v>27/9 2026</v>
@@ -11292,7 +11292,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E432" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F432" s="1">
         <v>46295</v>
